--- a/reviews/a-envoyer/la-galerie-immobiliere-2026-10-12.xlsx
+++ b/reviews/a-envoyer/la-galerie-immobiliere-2026-10-12.xlsx
@@ -855,7 +855,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-09T06:15:38</t>
+          <t>2026-10-09T11:44:28</t>
         </is>
       </c>
     </row>
